--- a/artfynd/A 58663-2024 artfynd.xlsx
+++ b/artfynd/A 58663-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13648794</v>
+        <v>104210954</v>
       </c>
       <c r="B2" t="n">
-        <v>24854</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101707</v>
+        <v>5966</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhithrogena germanica</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Eaton, 1885</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gagnån, Fagerhult, Vg</t>
+          <t>Baskarp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448934.9113702015</v>
+        <v>449059</v>
       </c>
       <c r="R2" t="n">
-        <v>6428565.139934073</v>
+        <v>6428432</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-12-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-12-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Provtagare: Per-Anders Nilsson, Metodik: SS-EN 27 828</t>
+          <t>Nära rutten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,38 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>vattendrag</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Liungman</t>
+          <t>Ida Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Martin Liungman</t>
+          <t>Ida Johansson, Morgan Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104210954</v>
+        <v>13648794</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>25167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,40 +792,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Motaggsvamp</t>
-        </is>
+        <v>101707</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Rhithrogena germanica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Eaton, 1885</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baskarp, Vg</t>
+          <t>Gagnån, Fagerhult, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449058.5495785907</v>
+        <v>448935</v>
       </c>
       <c r="R3" t="n">
-        <v>6428431.56235252</v>
+        <v>6428565</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,27 +850,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-12-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-12-29</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Nära rutten</t>
+          <t>Provtagare: Per-Anders Nilsson, Metodik: SS-EN 27 828</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,19 +869,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>vattendrag</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ida Johansson</t>
+          <t>Martin Liungman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ida Johansson, Morgan Johansson</t>
+          <t>Via Martin Liungman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 58663-2024 artfynd.xlsx
+++ b/artfynd/A 58663-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104210954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,8 +899,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13648794</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>